--- a/public/assets/8 - ANNEXE VI.1 - EPREUVE E5 TABLEAU DE SYNTHESE - BTS SIO 2026.xlsx
+++ b/public/assets/8 - ANNEXE VI.1 - EPREUVE E5 TABLEAU DE SYNTHESE - BTS SIO 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zarath\Bureau\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b144e573caf0f44/Bureau/Portfolio-BTSSIO - Copie/public/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A94931-F652-4FF5-91A2-EBD7B29FFD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DF939DC-FAF7-44D1-97DB-AC5E0B8500B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,9 +48,6 @@
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Option :</t>
   </si>
   <si>
@@ -179,6 +176,9 @@
   </si>
   <si>
     <t>Adresse URL du portfolio : https://zarathmgd.github.io/Portfolio-BTSSIO/</t>
+  </si>
+  <si>
+    <t>N° candidat : 02545812866</t>
   </si>
 </sst>
 </file>
@@ -664,9 +664,57 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -689,54 +737,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1127,124 +1127,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="20"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="22"/>
-      <c r="H3" s="28"/>
+      <c r="A3" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="38"/>
+      <c r="H3" s="44"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="14" t="s">
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="29" t="s">
+      <c r="B6" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="7" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="21"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="30"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="15" t="s">
+      <c r="D7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="F7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="G7" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>19</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>20</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1283,16 +1283,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33"/>
+      <c r="A8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="25"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1331,17 +1331,17 @@
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H9" s="19"/>
       <c r="I9"/>
@@ -1382,19 +1382,19 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
       <c r="F10" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10" s="19"/>
       <c r="I10"/>
@@ -1435,17 +1435,17 @@
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="17"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
       <c r="F11" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11" s="19"/>
       <c r="I11"/>
@@ -1486,17 +1486,17 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12"/>
@@ -1537,19 +1537,19 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13"/>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="18"/>
@@ -1779,7 +1779,7 @@
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
       <c r="H18" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -1818,16 +1818,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36"/>
+      <c r="A19" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="28"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1866,14 +1866,14 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20" s="17"/>
       <c r="C20" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
@@ -1917,19 +1917,19 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18"/>
       <c r="F21" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H21" s="19"/>
       <c r="I21"/>
@@ -1970,17 +1970,17 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
       <c r="F22" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H22" s="19"/>
       <c r="I22"/>
@@ -2021,19 +2021,19 @@
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="18"/>
       <c r="F23" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23"/>
@@ -2074,17 +2074,17 @@
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
       <c r="E24" s="18"/>
       <c r="F24" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H24" s="19"/>
       <c r="I24"/>
@@ -2170,18 +2170,18 @@
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
       <c r="E26" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" s="18"/>
       <c r="G26" s="18"/>
       <c r="H26" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -2220,16 +2220,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A27" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
+      <c r="A27" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="31"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2268,14 +2268,14 @@
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="17"/>
       <c r="C28" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
@@ -2319,17 +2319,17 @@
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="17"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
       <c r="E29" s="18"/>
       <c r="F29" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H29" s="19"/>
       <c r="I29"/>
@@ -2370,19 +2370,19 @@
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H30" s="19"/>
       <c r="I30"/>
@@ -2558,18 +2558,18 @@
     </row>
     <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" s="17"/>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
       <c r="E34" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F34" s="18"/>
       <c r="G34" s="18"/>
       <c r="H34" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
@@ -2700,6 +2700,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2707,11 +2712,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2723,15 +2723,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="aa2ece9c-98a3-498c-b019-c92ebab19525">
@@ -2740,6 +2731,15 @@
     <TaxCatchAll xmlns="61a7795e-c37a-4ca4-ab9f-176b7c7c4f4d" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2938,20 +2938,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8343CED-E802-4DDF-9711-46BA9FD51DCD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7943F7E5-D07F-41AD-8098-267818EB5DAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="aa2ece9c-98a3-498c-b019-c92ebab19525"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="61a7795e-c37a-4ca4-ab9f-176b7c7c4f4d"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7943F7E5-D07F-41AD-8098-267818EB5DAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8343CED-E802-4DDF-9711-46BA9FD51DCD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="aa2ece9c-98a3-498c-b019-c92ebab19525"/>
-    <ds:schemaRef ds:uri="61a7795e-c37a-4ca4-ab9f-176b7c7c4f4d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
